--- a/artfynd/A 58835-2021 artfynd.xlsx
+++ b/artfynd/A 58835-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58835-2021 artfynd.xlsx
+++ b/artfynd/A 58835-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>160550</v>
+        <v>140950</v>
       </c>
       <c r="B2" t="n">
-        <v>85702</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>808992.6142262351</v>
+        <v>808993</v>
       </c>
       <c r="R2" t="n">
-        <v>7156535.697479819</v>
+        <v>7156536</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>140950</v>
+        <v>160550</v>
       </c>
       <c r="B3" t="n">
-        <v>89337</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>808992.6142262351</v>
+        <v>808993</v>
       </c>
       <c r="R3" t="n">
-        <v>7156535.697479819</v>
+        <v>7156536</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>391081</v>
+        <v>415322</v>
       </c>
       <c r="B4" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808992.6142262351</v>
+        <v>808993</v>
       </c>
       <c r="R4" t="n">
-        <v>7156535.697479819</v>
+        <v>7156536</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>415322</v>
+        <v>391081</v>
       </c>
       <c r="B5" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808992.6142262351</v>
+        <v>808993</v>
       </c>
       <c r="R5" t="n">
-        <v>7156535.697479819</v>
+        <v>7156536</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58835-2021 artfynd.xlsx
+++ b/artfynd/A 58835-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/140950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/160550</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/415322</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/391081</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>